--- a/Employee_Reports_wi48/Pubudu Maduranga Hearth Ralalage Q0134.xlsx
+++ b/Employee_Reports_wi48/Pubudu Maduranga Hearth Ralalage Q0134.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1854,11 +1854,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1977,11 +1977,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
